--- a/demo_data/sectors/uretim_sanayi/inventory.xlsx
+++ b/demo_data/sectors/uretim_sanayi/inventory.xlsx
@@ -476,13 +476,13 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>1048.11</v>
+        <v>1049.45</v>
       </c>
       <c r="D2" t="n">
         <v>450</v>
       </c>
       <c r="E2" t="n">
-        <v>471649.5</v>
+        <v>472254.62</v>
       </c>
       <c r="F2" s="2" t="n">
         <v>45977</v>
